--- a/excel/dictionaries/nba_2008-2025_dictionary.xlsx
+++ b/excel/dictionaries/nba_2008-2025_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\COSC301\Project\DataPipeline\excel\dictionaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF46DE7-C660-4C93-9B74-FB612723C24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4685910F-BE8A-42A8-B726-7DB19285B0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B724BAFF-B4A6-4F01-86E5-962F2D3C616F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{B724BAFF-B4A6-4F01-86E5-962F2D3C616F}"/>
   </bookViews>
   <sheets>
     <sheet name="CleaningDictionary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="132">
   <si>
     <t>Column</t>
   </si>
@@ -227,14 +227,232 @@
     <t>Value will be '1' if more points were scored than the total
 Value will be '0' if less points were scored than the total
 Value will be '2' if the value in total was matched by the amount of points scored in the game</t>
+  </si>
+  <si>
+    <t>**Derived Columns**</t>
+  </si>
+  <si>
+    <t>How it was Made</t>
+  </si>
+  <si>
+    <t>days_rest_home</t>
+  </si>
+  <si>
+    <t>Days since last game played by home team</t>
+  </si>
+  <si>
+    <t>days_rest_away</t>
+  </si>
+  <si>
+    <t>Days since last game played by away team</t>
+  </si>
+  <si>
+    <t>Analyze potential relationship between rest days and performance</t>
+  </si>
+  <si>
+    <t>Iterate over games find when last one was played. Cap at 5</t>
+  </si>
+  <si>
+    <t>See if playing more tired affects result</t>
+  </si>
+  <si>
+    <t>last_game_ot_home</t>
+  </si>
+  <si>
+    <t>True if the home team's last game went to overtime</t>
+  </si>
+  <si>
+    <t>Iterate over games, find if last game played by home team went to overtime</t>
+  </si>
+  <si>
+    <t>last_game_ot_away</t>
+  </si>
+  <si>
+    <t>True if the away team's last game went to overtime</t>
+  </si>
+  <si>
+    <t>Iterate over games, find if last game played by away team went to overtime</t>
+  </si>
+  <si>
+    <t>win_loss_home</t>
+  </si>
+  <si>
+    <t>win_loss_away</t>
+  </si>
+  <si>
+    <t>last10_win_loss_home</t>
+  </si>
+  <si>
+    <t>last10_win_loss_away</t>
+  </si>
+  <si>
+    <t>Win Loss Record for current season for home team (stored as W-L)</t>
+  </si>
+  <si>
+    <t>Win Loss Record for last 10 games for home team (stored as W-L)</t>
+  </si>
+  <si>
+    <t>Get game result, update record based on last game the team has played</t>
+  </si>
+  <si>
+    <t>Get game result, update record based on last game the team has played, as well as 10 games ago</t>
+  </si>
+  <si>
+    <t>Good metric for how good the team is</t>
+  </si>
+  <si>
+    <t>Has the team been playing well recently?</t>
+  </si>
+  <si>
+    <t>west_conference_home</t>
+  </si>
+  <si>
+    <t>west_conference_away</t>
+  </si>
+  <si>
+    <t>True if team plays in western conference, false if team plays in the east</t>
+  </si>
+  <si>
+    <t>Manual mapping</t>
+  </si>
+  <si>
+    <t>There is often a difference in strength of conferences</t>
+  </si>
+  <si>
+    <t>home_record</t>
+  </si>
+  <si>
+    <t>away_record</t>
+  </si>
+  <si>
+    <t>The home team's record when they play at home</t>
+  </si>
+  <si>
+    <t>The away team's record when they play on the road</t>
+  </si>
+  <si>
+    <t>Callback to team's last home game</t>
+  </si>
+  <si>
+    <t>Callback to team's last away game</t>
+  </si>
+  <si>
+    <t>Home court advantage</t>
+  </si>
+  <si>
+    <t>implied_odds_home</t>
+  </si>
+  <si>
+    <t>implied_odds_away</t>
+  </si>
+  <si>
+    <t>Based on the moneyline, the odds a team is given to win the game</t>
+  </si>
+  <si>
+    <t>For favorites: |M| / (|M| + 100) For underdogs: 100 / (M + 100) -- M = moneyline</t>
+  </si>
+  <si>
+    <t>Our regression model will give the probability a team wins a game.</t>
+  </si>
+  <si>
+    <t>profit_moneyline_home</t>
+  </si>
+  <si>
+    <t>profit_moneyline_away</t>
+  </si>
+  <si>
+    <t>What would be your profit if you bet $10 on this team to win every game this year</t>
+  </si>
+  <si>
+    <t>Use same formula as above to calculate return if the bet would have hit, sum for full year</t>
+  </si>
+  <si>
+    <t>Are some teams over/undervalued?</t>
+  </si>
+  <si>
+    <t>points_for_home</t>
+  </si>
+  <si>
+    <t>points_for_away</t>
+  </si>
+  <si>
+    <t>points_against_home</t>
+  </si>
+  <si>
+    <t>points_against_away</t>
+  </si>
+  <si>
+    <t>points_for_last10_home</t>
+  </si>
+  <si>
+    <t>points_for_last10_away</t>
+  </si>
+  <si>
+    <t>points_against_last10_home</t>
+  </si>
+  <si>
+    <t>points_against_last10_away</t>
+  </si>
+  <si>
+    <t>Average number of points scored by the home team this season</t>
+  </si>
+  <si>
+    <t>Average number of points scored by the away team this season</t>
+  </si>
+  <si>
+    <t>Average number of points allowed by the home team this season</t>
+  </si>
+  <si>
+    <t>Average number of points allowed by the away team this season</t>
+  </si>
+  <si>
+    <t>Average number of points scored by the home team over the last 10 games</t>
+  </si>
+  <si>
+    <t>Average number of points scored by the away team over the last 10 games</t>
+  </si>
+  <si>
+    <t>Average number of points allowed by the home team over the last 10 games</t>
+  </si>
+  <si>
+    <t>Average number of points allowed by the away team over the last 10 games</t>
+  </si>
+  <si>
+    <t>Measures a team's offense this season</t>
+  </si>
+  <si>
+    <t>Measures a team's offense over the last 10 games</t>
+  </si>
+  <si>
+    <t>Measures a team's defense this season</t>
+  </si>
+  <si>
+    <t>Measures a team's defense over the last 10 games</t>
+  </si>
+  <si>
+    <t>Measures a team's defense ove the last 10 games</t>
+  </si>
+  <si>
+    <t>Rolling calculation</t>
+  </si>
+  <si>
+    <t>nba_2008-2025_extended.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -262,11 +480,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,16 +830,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -981,9 +1200,735 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527348B7-8223-463B-82A3-4681F2068E33}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="78.77734375" customWidth="1"/>
+    <col min="3" max="3" width="83.5546875" customWidth="1"/>
+    <col min="4" max="4" width="61.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>